--- a/packages/GB Accounts Company 2020-12-31 (Dec20) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2020-12-31 (Dec20) Excel 2007/Financialaccounts.xlsx
@@ -16291,7 +16291,7 @@
       <c r="A2" s="253"/>
       <c r="B2" s="329">
         <f>DATE(YEAR(B4),MONTH(B4),1)-1</f>
-        <v>45657</v>
+        <v>43738</v>
       </c>
       <c r="C2" s="253"/>
       <c r="D2" s="634"/>
@@ -16313,7 +16313,7 @@
       <c r="A3" s="253"/>
       <c r="B3" s="330">
         <f>DATE(YEAR(B4),MONTH(B4),1)</f>
-        <v>45658</v>
+        <v>43739</v>
       </c>
       <c r="C3" s="253"/>
       <c r="D3" s="635" t="s">
@@ -16345,7 +16345,7 @@
       <c r="A4" s="253"/>
       <c r="B4" s="330">
         <f>DATE(YEAR(B6),MONTH(B6),1)-1</f>
-        <v>45688</v>
+        <v>43769</v>
       </c>
       <c r="C4" s="253"/>
       <c r="D4" s="253"/>
@@ -16371,7 +16371,7 @@
       <c r="A5" s="253"/>
       <c r="B5" s="330">
         <f>DATE(YEAR(B6),MONTH(B6),1)</f>
-        <v>45689</v>
+        <v>43770</v>
       </c>
       <c r="C5" s="253"/>
       <c r="D5" s="253" t="s">
@@ -16402,7 +16402,7 @@
       <c r="A6" s="253"/>
       <c r="B6" s="330">
         <f>DATE(YEAR(B8),MONTH(B8),1)-1</f>
-        <v>45716</v>
+        <v>43799</v>
       </c>
       <c r="C6" s="253"/>
       <c r="D6" s="253" t="s">
@@ -16446,7 +16446,7 @@
       <c r="A7" s="253"/>
       <c r="B7" s="330">
         <f>DATE(YEAR(B8),MONTH(B8),1)</f>
-        <v>45717</v>
+        <v>43800</v>
       </c>
       <c r="C7" s="253"/>
       <c r="D7" s="253" t="s">
@@ -16490,7 +16490,7 @@
       <c r="A8" s="253"/>
       <c r="B8" s="330">
         <f>DATE(YEAR(B10),MONTH(B10),1)-1</f>
-        <v>45747</v>
+        <v>43830</v>
       </c>
       <c r="C8" s="253"/>
       <c r="D8" s="253" t="s">
@@ -16519,7 +16519,7 @@
       <c r="A9" s="253"/>
       <c r="B9" s="330">
         <f>DATE(YEAR(B10),MONTH(B10),1)</f>
-        <v>45748</v>
+        <v>43831</v>
       </c>
       <c r="C9" s="253"/>
       <c r="D9" s="253"/>
@@ -16545,7 +16545,7 @@
       <c r="A10" s="253"/>
       <c r="B10" s="330">
         <f>DATE(YEAR(B12),MONTH(B12),1)-1</f>
-        <v>45777</v>
+        <v>43861</v>
       </c>
       <c r="C10" s="253"/>
       <c r="D10" s="637" t="s">
@@ -16577,7 +16577,7 @@
       <c r="A11" s="253"/>
       <c r="B11" s="330">
         <f>DATE(YEAR(B12),MONTH(B12),1)</f>
-        <v>45778</v>
+        <v>43862</v>
       </c>
       <c r="C11" s="253"/>
       <c r="D11" s="253" t="s">
@@ -16615,7 +16615,7 @@
       <c r="A12" s="253"/>
       <c r="B12" s="330">
         <f>DATE(YEAR(B14),MONTH(B14),1)-1</f>
-        <v>45808</v>
+        <v>43890</v>
       </c>
       <c r="C12" s="253"/>
       <c r="D12" s="253"/>
@@ -16637,7 +16637,7 @@
       <c r="A13" s="253"/>
       <c r="B13" s="330">
         <f>DATE(YEAR(B14),MONTH(B14),1)</f>
-        <v>45809</v>
+        <v>43891</v>
       </c>
       <c r="C13" s="253"/>
       <c r="D13" s="635" t="s">
@@ -16663,7 +16663,7 @@
       <c r="A14" s="253"/>
       <c r="B14" s="330">
         <f>DATE(YEAR(B16),MONTH(B16),1)-1</f>
-        <v>45838</v>
+        <v>43921</v>
       </c>
       <c r="C14" s="253"/>
       <c r="D14" s="253"/>
@@ -16691,7 +16691,7 @@
       <c r="A15" s="253"/>
       <c r="B15" s="330">
         <f>DATE(YEAR(B16),MONTH(B16),1)</f>
-        <v>45839</v>
+        <v>43922</v>
       </c>
       <c r="C15" s="253"/>
       <c r="D15" s="637" t="s">
@@ -16717,7 +16717,7 @@
       <c r="A16" s="253"/>
       <c r="B16" s="330">
         <f>DATE(YEAR(B18),MONTH(B18),1)-1</f>
-        <v>45869</v>
+        <v>43951</v>
       </c>
       <c r="C16" s="253"/>
       <c r="D16" s="637" t="s">
@@ -16749,7 +16749,7 @@
       <c r="A17" s="253"/>
       <c r="B17" s="330">
         <f>DATE(YEAR(B18),MONTH(B18),1)</f>
-        <v>45870</v>
+        <v>43952</v>
       </c>
       <c r="C17" s="253"/>
       <c r="D17" s="637" t="s">
@@ -16781,7 +16781,7 @@
       <c r="A18" s="253"/>
       <c r="B18" s="330">
         <f>DATE(YEAR(B20),MONTH(B20),1)-1</f>
-        <v>45900</v>
+        <v>43982</v>
       </c>
       <c r="C18" s="253"/>
       <c r="D18" s="637" t="s">
@@ -16807,7 +16807,7 @@
       <c r="A19" s="253"/>
       <c r="B19" s="330">
         <f>DATE(YEAR(B20),MONTH(B20),1)</f>
-        <v>45901</v>
+        <v>43983</v>
       </c>
       <c r="C19" s="253"/>
       <c r="D19" s="637" t="s">
@@ -16843,7 +16843,7 @@
       <c r="A20" s="253"/>
       <c r="B20" s="330">
         <f>DATE(YEAR(B22),MONTH(B22),1)-1</f>
-        <v>45930</v>
+        <v>44012</v>
       </c>
       <c r="C20" s="253"/>
       <c r="D20" s="253"/>
@@ -16865,7 +16865,7 @@
       <c r="A21" s="253"/>
       <c r="B21" s="330">
         <f>DATE(YEAR(B22),MONTH(B22),1)</f>
-        <v>45931</v>
+        <v>44013</v>
       </c>
       <c r="C21" s="253"/>
       <c r="D21" s="9" t="s">
@@ -16898,7 +16898,7 @@
       <c r="A22" s="253"/>
       <c r="B22" s="330">
         <f>DATE(YEAR(B24),MONTH(B24),1)-1</f>
-        <v>45961</v>
+        <v>44043</v>
       </c>
       <c r="C22" s="253"/>
       <c r="D22" s="253"/>
@@ -16920,7 +16920,7 @@
       <c r="A23" s="253"/>
       <c r="B23" s="330">
         <f>DATE(YEAR(B24),MONTH(B24),1)</f>
-        <v>45962</v>
+        <v>44044</v>
       </c>
       <c r="C23" s="253"/>
       <c r="F23" s="293"/>
@@ -16929,7 +16929,7 @@
       <c r="A24" s="253"/>
       <c r="B24" s="330">
         <f>DATE(YEAR(B26),MONTH(B26),1)-1</f>
-        <v>45991</v>
+        <v>44074</v>
       </c>
       <c r="C24" s="253"/>
     </row>
@@ -16937,7 +16937,7 @@
       <c r="A25" s="253"/>
       <c r="B25" s="330">
         <f>DATE(YEAR(B26),MONTH(B26),1)</f>
-        <v>45992</v>
+        <v>44075</v>
       </c>
       <c r="C25" s="253"/>
       <c r="F25" s="267"/>
@@ -16947,7 +16947,7 @@
       <c r="A26" s="253"/>
       <c r="B26" s="330">
         <f>DATE(YEAR(B28),MONTH(B28),1)-1</f>
-        <v>46022</v>
+        <v>44104</v>
       </c>
       <c r="C26" s="253"/>
       <c r="G26" s="256"/>
@@ -16956,7 +16956,7 @@
       <c r="A27" s="253"/>
       <c r="B27" s="330">
         <f>DATE(YEAR(B28),MONTH(B28),1)</f>
-        <v>46023</v>
+        <v>44105</v>
       </c>
       <c r="C27" s="253"/>
       <c r="G27" s="256"/>
@@ -16965,7 +16965,7 @@
       <c r="A28" s="253"/>
       <c r="B28" s="330">
         <f>DATE(YEAR(B30),MONTH(B30),1)-1</f>
-        <v>46053</v>
+        <v>44135</v>
       </c>
       <c r="C28" s="253"/>
     </row>
@@ -16973,7 +16973,7 @@
       <c r="A29" s="253"/>
       <c r="B29" s="330">
         <f>DATE(YEAR(B30),MONTH(B30),1)</f>
-        <v>46054</v>
+        <v>44136</v>
       </c>
       <c r="C29" s="253"/>
     </row>
@@ -16981,7 +16981,7 @@
       <c r="A30" s="253"/>
       <c r="B30" s="330">
         <f>DATE(YEAR(B32),MONTH(B32),1)-1</f>
-        <v>46081</v>
+        <v>44165</v>
       </c>
       <c r="C30" s="253"/>
     </row>
@@ -16989,7 +16989,7 @@
       <c r="A31" s="253"/>
       <c r="B31" s="330">
         <f>DATE(YEAR(B32),MONTH(B32),1)</f>
-        <v>46082</v>
+        <v>44166</v>
       </c>
       <c r="C31" s="253"/>
     </row>
@@ -16997,7 +16997,7 @@
       <c r="A32" s="253"/>
       <c r="B32" s="331">
         <f>F21</f>
-        <v>46112</v>
+        <v>44196</v>
       </c>
       <c r="C32" s="253"/>
     </row>
@@ -17005,7 +17005,7 @@
       <c r="A33" s="253"/>
       <c r="B33" s="330">
         <f>DATE(YEAR(B34),MONTH(B34),1)</f>
-        <v>46113</v>
+        <v>44197</v>
       </c>
       <c r="C33" s="253"/>
     </row>
@@ -17013,7 +17013,7 @@
       <c r="A34" s="253"/>
       <c r="B34" s="330">
         <f>DATE(IF(MONTH(B32)&lt;11,YEAR(B32),YEAR(B32)+1),IF(MONTH(B32)&lt;11,MONTH(B32)+2,IF(MONTH(B32)=11,1,2)),1)-1</f>
-        <v>46142</v>
+        <v>44227</v>
       </c>
       <c r="C34" s="253"/>
     </row>
@@ -17021,7 +17021,7 @@
       <c r="A35" s="253"/>
       <c r="B35" s="330">
         <f>DATE(YEAR(B36),MONTH(B36),1)</f>
-        <v>46143</v>
+        <v>44228</v>
       </c>
       <c r="C35" s="253"/>
     </row>
@@ -17029,7 +17029,7 @@
       <c r="A36" s="253"/>
       <c r="B36" s="330">
         <f>DATE(IF(MONTH(B34)&lt;11,YEAR(B34),YEAR(B34)+1),IF(MONTH(B34)&lt;11,MONTH(B34)+2,IF(MONTH(B34)=11,1,2)),1)-1</f>
-        <v>46173</v>
+        <v>44255</v>
       </c>
       <c r="C36" s="253"/>
     </row>
@@ -17037,7 +17037,7 @@
       <c r="A37" s="253"/>
       <c r="B37" s="330">
         <f>DATE(YEAR(B38),MONTH(B38),1)</f>
-        <v>46174</v>
+        <v>44256</v>
       </c>
       <c r="C37" s="253"/>
     </row>
@@ -17045,7 +17045,7 @@
       <c r="A38" s="253"/>
       <c r="B38" s="330">
         <f>DATE(IF(MONTH(B36)&lt;11,YEAR(B36),YEAR(B36)+1),IF(MONTH(B36)&lt;11,MONTH(B36)+2,IF(MONTH(B36)=11,1,2)),1)-1</f>
-        <v>46203</v>
+        <v>44286</v>
       </c>
       <c r="C38" s="253"/>
     </row>
@@ -17053,7 +17053,7 @@
       <c r="A39" s="253"/>
       <c r="B39" s="330">
         <f>DATE(YEAR(B40),MONTH(B40),1)</f>
-        <v>46204</v>
+        <v>44287</v>
       </c>
       <c r="C39" s="253"/>
     </row>
@@ -17061,7 +17061,7 @@
       <c r="A40" s="253"/>
       <c r="B40" s="330">
         <f>DATE(IF(MONTH(B38)&lt;11,YEAR(B38),YEAR(B38)+1),IF(MONTH(B38)&lt;11,MONTH(B38)+2,IF(MONTH(B38)=11,1,2)),1)-1</f>
-        <v>46234</v>
+        <v>44316</v>
       </c>
       <c r="C40" s="253"/>
     </row>
@@ -17069,7 +17069,7 @@
       <c r="A41" s="253"/>
       <c r="B41" s="330">
         <f>DATE(YEAR(B42),MONTH(B42),1)</f>
-        <v>46235</v>
+        <v>44317</v>
       </c>
       <c r="C41" s="253"/>
     </row>
@@ -17077,7 +17077,7 @@
       <c r="A42" s="253"/>
       <c r="B42" s="330">
         <f>DATE(IF(MONTH(B40)&lt;11,YEAR(B40),YEAR(B40)+1),IF(MONTH(B40)&lt;11,MONTH(B40)+2,IF(MONTH(B40)=11,1,2)),1)-1</f>
-        <v>46265</v>
+        <v>44347</v>
       </c>
       <c r="C42" s="253"/>
     </row>
@@ -17085,7 +17085,7 @@
       <c r="A43" s="253"/>
       <c r="B43" s="330">
         <f>DATE(YEAR(B44),MONTH(B44),1)</f>
-        <v>46266</v>
+        <v>44348</v>
       </c>
       <c r="C43" s="253"/>
     </row>
@@ -17093,7 +17093,7 @@
       <c r="A44" s="253"/>
       <c r="B44" s="330">
         <f>DATE(IF(MONTH(B42)&lt;11,YEAR(B42),YEAR(B42)+1),IF(MONTH(B42)&lt;11,MONTH(B42)+2,IF(MONTH(B42)=11,1,2)),1)-1</f>
-        <v>46295</v>
+        <v>44377</v>
       </c>
       <c r="C44" s="253"/>
     </row>
@@ -17101,7 +17101,7 @@
       <c r="A45" s="253"/>
       <c r="B45" s="330">
         <f>DATE(YEAR(B46),MONTH(B46),1)</f>
-        <v>46296</v>
+        <v>44378</v>
       </c>
       <c r="C45" s="253"/>
     </row>
@@ -17109,7 +17109,7 @@
       <c r="A46" s="253"/>
       <c r="B46" s="330">
         <f>DATE(IF(MONTH(B44)&lt;11,YEAR(B44),YEAR(B44)+1),IF(MONTH(B44)&lt;11,MONTH(B44)+2,IF(MONTH(B44)=11,1,2)),1)-1</f>
-        <v>46326</v>
+        <v>44408</v>
       </c>
       <c r="C46" s="253"/>
     </row>
@@ -17117,7 +17117,7 @@
       <c r="A47" s="253"/>
       <c r="B47" s="330">
         <f>DATE(YEAR(B48),MONTH(B48),1)</f>
-        <v>46327</v>
+        <v>44409</v>
       </c>
       <c r="C47" s="253"/>
     </row>
@@ -17125,7 +17125,7 @@
       <c r="A48" s="253"/>
       <c r="B48" s="330">
         <f>DATE(IF(MONTH(B46)&lt;11,YEAR(B46),YEAR(B46)+1),IF(MONTH(B46)&lt;11,MONTH(B46)+2,IF(MONTH(B46)=11,1,2)),1)-1</f>
-        <v>46356</v>
+        <v>44439</v>
       </c>
       <c r="C48" s="253"/>
     </row>
@@ -17133,7 +17133,7 @@
       <c r="A49" s="253"/>
       <c r="B49" s="330">
         <f>DATE(YEAR(B50),MONTH(B50),1)</f>
-        <v>46357</v>
+        <v>44440</v>
       </c>
       <c r="C49" s="253"/>
     </row>
@@ -17141,7 +17141,7 @@
       <c r="A50" s="253"/>
       <c r="B50" s="330">
         <f>DATE(IF(MONTH(B48)&lt;11,YEAR(B48),YEAR(B48)+1),IF(MONTH(B48)&lt;11,MONTH(B48)+2,IF(MONTH(B48)=11,1,2)),1)-1</f>
-        <v>46387</v>
+        <v>44469</v>
       </c>
       <c r="C50" s="253"/>
     </row>
@@ -17149,7 +17149,7 @@
       <c r="A51" s="253"/>
       <c r="B51" s="330">
         <f>DATE(YEAR(B52),MONTH(B52),1)</f>
-        <v>46388</v>
+        <v>44470</v>
       </c>
       <c r="C51" s="253"/>
     </row>
@@ -17157,7 +17157,7 @@
       <c r="A52" s="253"/>
       <c r="B52" s="330">
         <f>DATE(IF(MONTH(B50)&lt;11,YEAR(B50),YEAR(B50)+1),IF(MONTH(B50)&lt;11,MONTH(B50)+2,IF(MONTH(B50)=11,1,2)),1)-1</f>
-        <v>46418</v>
+        <v>44500</v>
       </c>
       <c r="C52" s="253"/>
     </row>
@@ -17165,7 +17165,7 @@
       <c r="A53" s="253"/>
       <c r="B53" s="330">
         <f>DATE(YEAR(B54),MONTH(B54),1)</f>
-        <v>46419</v>
+        <v>44501</v>
       </c>
       <c r="C53" s="253"/>
     </row>
@@ -17173,7 +17173,7 @@
       <c r="A54" s="253"/>
       <c r="B54" s="330">
         <f>DATE(IF(MONTH(B52)&lt;11,YEAR(B52),YEAR(B52)+1),IF(MONTH(B52)&lt;11,MONTH(B52)+2,IF(MONTH(B52)=11,1,2)),1)-1</f>
-        <v>46446</v>
+        <v>44530</v>
       </c>
       <c r="C54" s="253"/>
     </row>
@@ -17181,7 +17181,7 @@
       <c r="A55" s="253"/>
       <c r="B55" s="330">
         <f>DATE(YEAR(B56),MONTH(B56),1)</f>
-        <v>46447</v>
+        <v>44531</v>
       </c>
       <c r="C55" s="253"/>
     </row>
@@ -17189,7 +17189,7 @@
       <c r="A56" s="253"/>
       <c r="B56" s="332">
         <f>DATE(IF(MONTH(B54)&lt;11,YEAR(B54),YEAR(B54)+1),IF(MONTH(B54)&lt;11,MONTH(B54)+2,IF(MONTH(B54)=11,1,2)),1)-1</f>
-        <v>46477</v>
+        <v>44561</v>
       </c>
       <c r="C56" s="253"/>
     </row>

--- a/packages/GB Accounts Company 2020-12-31 (Dec20) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2020-12-31 (Dec20) Excel 2007/Financialaccounts.xlsx
@@ -12979,7 +12979,7 @@
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="11">
-        <f>E15</f>
+        <f>IF(COUNT(E43:E47,E49:E76,E80:E85)=0,0,E15)</f>
         <v>0</v>
       </c>
       <c r="F48" s="3"/>
@@ -16422,17 +16422,17 @@
       </c>
       <c r="J6" s="185"/>
       <c r="K6" s="185">
-        <f>YEAR(L6)</f>
-        <v>2025</v>
+        <f>YEAR(L6)-IF(MONTH(L6)&lt;4,1,0)</f>
+        <v>2019</v>
       </c>
       <c r="L6" s="638">
         <f>B9</f>
-        <v>45748</v>
+        <v>43831</v>
       </c>
       <c r="M6" s="639"/>
       <c r="N6" s="638">
-        <f>B32</f>
-        <v>46112</v>
+        <f>MIN(IF(DATE(YEAR(L6),3,31)&gt;=L6,DATE(YEAR(L6),3,31),DATE(YEAR(L6)+1,3,31)),F21)</f>
+        <v>43921</v>
       </c>
       <c r="O6" s="641"/>
       <c r="P6" s="310">
@@ -16466,17 +16466,17 @@
       </c>
       <c r="J7" s="185"/>
       <c r="K7" s="185">
-        <f>YEAR(L7)</f>
-        <v>2026</v>
+        <f>YEAR(L7)-IF(MONTH(L7)&lt;4,1,0)</f>
+        <v>2020</v>
       </c>
       <c r="L7" s="638">
-        <f>B33</f>
-        <v>46113</v>
+        <f>N6+1</f>
+        <v>43922</v>
       </c>
       <c r="M7" s="639"/>
       <c r="N7" s="638">
-        <f>B56</f>
-        <v>46477</v>
+        <f>F21</f>
+        <v>44196</v>
       </c>
       <c r="O7" s="641"/>
       <c r="P7" s="310">
@@ -16505,15 +16505,23 @@
         <v>18</v>
       </c>
       <c r="H8" s="253"/>
-      <c r="I8" s="253"/>
+      <c r="I8" s="185" t="inlineStr">
+        <is>
+          <t>Corporation Tax main rate</t>
+        </is>
+      </c>
       <c r="J8" s="253"/>
       <c r="K8" s="253"/>
       <c r="L8" s="253"/>
       <c r="M8" s="253"/>
       <c r="N8" s="253"/>
       <c r="O8" s="253"/>
-      <c r="P8" s="255"/>
-      <c r="Q8" s="255"/>
+      <c r="P8" s="310">
+        <v>19</v>
+      </c>
+      <c r="Q8" s="255" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="9" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="253"/>
@@ -16527,7 +16535,11 @@
       <c r="F9" s="253"/>
       <c r="G9" s="255"/>
       <c r="H9" s="253"/>
-      <c r="I9" s="253"/>
+      <c r="I9" s="185" t="inlineStr">
+        <is>
+          <t>Marginal relief fraction</t>
+        </is>
+      </c>
       <c r="J9" s="253"/>
       <c r="K9" s="253"/>
       <c r="L9" s="262" t="s">
@@ -16538,7 +16550,9 @@
         <v>521</v>
       </c>
       <c r="O9" s="263"/>
-      <c r="P9" s="264"/>
+      <c r="P9" s="262">
+        <v>0</v>
+      </c>
       <c r="Q9" s="255"/>
     </row>
     <row r="10" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16623,14 +16637,20 @@
       <c r="F12" s="253"/>
       <c r="G12" s="255"/>
       <c r="H12" s="253"/>
-      <c r="I12" s="253"/>
+      <c r="I12" s="185" t="inlineStr">
+        <is>
+          <t>Marginal relief lower limit</t>
+        </is>
+      </c>
       <c r="J12" s="253"/>
       <c r="K12" s="253"/>
       <c r="L12" s="253"/>
       <c r="M12" s="265"/>
       <c r="N12" s="255"/>
       <c r="O12" s="253"/>
-      <c r="P12" s="255"/>
+      <c r="P12" s="262">
+        <v>0</v>
+      </c>
       <c r="Q12" s="255"/>
     </row>
     <row r="13" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16649,14 +16669,20 @@
         <v>268</v>
       </c>
       <c r="H13" s="253"/>
-      <c r="I13" s="253"/>
+      <c r="I13" s="185" t="inlineStr">
+        <is>
+          <t>Marginal relief upper limit</t>
+        </is>
+      </c>
       <c r="J13" s="253"/>
       <c r="K13" s="253"/>
       <c r="L13" s="253"/>
       <c r="M13" s="253"/>
       <c r="N13" s="253"/>
       <c r="O13" s="253"/>
-      <c r="P13" s="253"/>
+      <c r="P13" s="262">
+        <v>0</v>
+      </c>
       <c r="Q13" s="253"/>
     </row>
     <row r="14" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -44960,22 +44986,28 @@
         <v>0</v>
       </c>
       <c r="G33" s="441">
-        <f>Admin!P6</f>
+        <f>IF(F33&lt;=Admin!$P$12*A33/A35,Admin!P6,Admin!$P$8)</f>
         <v>19</v>
       </c>
       <c r="H33" s="442"/>
       <c r="I33" s="187">
+        <f>J33-L33</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="167">
         <f>F33*G33/100</f>
         <v>0</v>
       </c>
-      <c r="J33" s="167"/>
       <c r="K33" s="161"/>
-      <c r="L33" s="38"/>
+      <c r="L33" s="38">
+        <f>IF(AND(F33&gt;Admin!$P$12*A33/A35,F33&lt;Admin!$P$13*A33/A35),(Admin!$P$13*A33/A35-F33)*Admin!$P$9,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="184">
-        <f>D34-C34+1</f>
-        <v>365</v>
+        <f>MAX(0,D34-C34+1)</f>
+        <v>0</v>
       </c>
       <c r="B34" s="182" t="s">
         <v>14</v>
@@ -44997,22 +45029,28 @@
         <v>0</v>
       </c>
       <c r="G34" s="441">
-        <f>Admin!P7</f>
+        <f>IF(F34&lt;=Admin!$P$12*A34/A35,Admin!P7,Admin!$P$8)</f>
         <v>19</v>
       </c>
       <c r="H34" s="442"/>
       <c r="I34" s="187">
+        <f>J34-L34</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="167">
         <f>F34*G34/100</f>
         <v>0</v>
       </c>
-      <c r="J34" s="167"/>
       <c r="K34" s="161"/>
-      <c r="L34" s="38"/>
+      <c r="L34" s="38">
+        <f>IF(AND(F34&gt;Admin!$P$12*A34/A35,F34&lt;Admin!$P$13*A34/A35),(Admin!$P$13*A34/A35-F34)*Admin!$P$9,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="35" spans="1:12" s="40" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A35" s="184">
         <f>D34-C33+1</f>
-        <v>730</v>
+        <v>365</v>
       </c>
       <c r="B35" s="157"/>
       <c r="C35" s="420" t="s">
@@ -52778,7 +52816,7 @@
         <v>150</v>
       </c>
       <c r="AJ126" s="535">
-        <f>CorporationTax!I33</f>
+        <f>CorporationTax!J33</f>
         <v>0</v>
       </c>
       <c r="AK126" s="535"/>
@@ -52843,12 +52881,15 @@
       <c r="B128" s="209">
         <v>53</v>
       </c>
-      <c r="C128" s="483"/>
-      <c r="D128" s="483"/>
-      <c r="E128" s="483"/>
-      <c r="F128" s="483"/>
-      <c r="G128" s="483"/>
-      <c r="H128" s="483"/>
+      <c r="C128" s="545" t="str">
+        <f>IF(CorporationTax!A34&gt;0,CorporationTax!E34," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="D128" s="546"/>
+      <c r="E128" s="546"/>
+      <c r="F128" s="546"/>
+      <c r="G128" s="546"/>
+      <c r="H128" s="547"/>
       <c r="I128" s="198"/>
       <c r="J128" s="198"/>
       <c r="K128" s="198"/>
@@ -52858,13 +52899,16 @@
       <c r="M128" s="210" t="s">
         <v>150</v>
       </c>
-      <c r="N128" s="483"/>
-      <c r="O128" s="483"/>
-      <c r="P128" s="483"/>
-      <c r="Q128" s="483"/>
-      <c r="R128" s="483"/>
-      <c r="S128" s="483"/>
-      <c r="T128" s="483"/>
+      <c r="N128" s="522" t="str">
+        <f>IF(CorporationTax!A34&gt;0,CorporationTax!F34," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="O128" s="468"/>
+      <c r="P128" s="468"/>
+      <c r="Q128" s="468"/>
+      <c r="R128" s="468"/>
+      <c r="S128" s="468"/>
+      <c r="T128" s="534"/>
       <c r="U128" s="198"/>
       <c r="V128" s="198"/>
       <c r="W128" s="198"/>
@@ -52873,8 +52917,11 @@
         <v>55</v>
       </c>
       <c r="Z128" s="351"/>
-      <c r="AA128" s="483"/>
-      <c r="AB128" s="483"/>
+      <c r="AA128" s="548" t="str">
+        <f>IF(CorporationTax!A34&gt;0,CorporationTax!G34," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="AB128" s="549"/>
       <c r="AC128" s="198"/>
       <c r="AD128" s="198"/>
       <c r="AE128" s="198"/>
@@ -52886,13 +52933,16 @@
       <c r="AI128" s="212" t="s">
         <v>150</v>
       </c>
-      <c r="AJ128" s="535"/>
-      <c r="AK128" s="468"/>
-      <c r="AL128" s="468"/>
-      <c r="AM128" s="468"/>
-      <c r="AN128" s="468"/>
-      <c r="AO128" s="468"/>
-      <c r="AP128" s="468"/>
+      <c r="AJ128" s="535">
+        <f>CorporationTax!J34</f>
+        <v>0</v>
+      </c>
+      <c r="AK128" s="535"/>
+      <c r="AL128" s="535"/>
+      <c r="AM128" s="535"/>
+      <c r="AN128" s="535"/>
+      <c r="AO128" s="535"/>
+      <c r="AP128" s="535"/>
       <c r="AQ128" s="224" t="s">
         <v>391</v>
       </c>
@@ -53130,11 +53180,14 @@
         <v>150</v>
       </c>
       <c r="X133" s="225"/>
-      <c r="Y133" s="514"/>
-      <c r="Z133" s="514"/>
-      <c r="AA133" s="514"/>
-      <c r="AB133" s="514"/>
-      <c r="AC133" s="514"/>
+      <c r="Y133" s="535">
+        <f>CorporationTax!L33+CorporationTax!L34</f>
+        <v>0</v>
+      </c>
+      <c r="Z133" s="535"/>
+      <c r="AA133" s="535"/>
+      <c r="AB133" s="535"/>
+      <c r="AC133" s="535"/>
       <c r="AD133" s="225"/>
       <c r="AE133" s="224" t="s">
         <v>391</v>
@@ -53232,11 +53285,14 @@
         <v>150</v>
       </c>
       <c r="X135" s="225"/>
-      <c r="Y135" s="514"/>
-      <c r="Z135" s="514"/>
-      <c r="AA135" s="514"/>
-      <c r="AB135" s="514"/>
-      <c r="AC135" s="514"/>
+      <c r="Y135" s="535">
+        <f>AJ131-Y133</f>
+        <v>0</v>
+      </c>
+      <c r="Z135" s="535"/>
+      <c r="AA135" s="535"/>
+      <c r="AB135" s="535"/>
+      <c r="AC135" s="535"/>
       <c r="AD135" s="225"/>
       <c r="AE135" s="224" t="s">
         <v>391</v>
@@ -53331,7 +53387,7 @@
         <v>66</v>
       </c>
       <c r="W137" s="543" t="str">
-        <f>IF(AJ131&gt;0,AJ131*100/AJ110," ")</f>
+        <f>IF(Y135&gt;0,Y135*100/AJ110," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="X137" s="544"/>
@@ -53753,7 +53809,7 @@
         <v>150</v>
       </c>
       <c r="AJ145" s="535">
-        <f>AJ131</f>
+        <f>Y135</f>
         <v>0</v>
       </c>
       <c r="AK145" s="468"/>

--- a/packages/GB Accounts Company 2020-12-31 (Dec20) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2020-12-31 (Dec20) Excel 2007/Financialaccounts.xlsx
@@ -16594,18 +16594,10 @@
         <v>43862</v>
       </c>
       <c r="C11" s="253"/>
-      <c r="D11" s="253" t="s">
-        <v>501</v>
-      </c>
-      <c r="E11" s="262">
-        <v>12000</v>
-      </c>
-      <c r="F11" s="253" t="s">
-        <v>502</v>
-      </c>
-      <c r="G11" s="262">
-        <v>3000</v>
-      </c>
+      <c r="D11" s="253"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="253"/>
+      <c r="G11" s="262"/>
       <c r="H11" s="253"/>
       <c r="I11" s="253"/>
       <c r="J11" s="253"/>
@@ -41121,7 +41113,7 @@
       </c>
       <c r="D3" s="281">
         <f>Admin!B32</f>
-        <v>46112</v>
+        <v>44196</v>
       </c>
       <c r="E3" s="67"/>
       <c r="H3" s="70"/>
@@ -41155,7 +41147,7 @@
       <c r="D5" s="81"/>
       <c r="E5" s="368">
         <f>D3</f>
-        <v>46112</v>
+        <v>44196</v>
       </c>
       <c r="F5" s="369"/>
       <c r="H5" s="70"/>
@@ -42231,7 +42223,7 @@
       </c>
       <c r="D2" s="285">
         <f>'PubP&amp;L'!D3</f>
-        <v>46112</v>
+        <v>44196</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
@@ -43150,7 +43142,7 @@
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" s="286">
         <f>'PubP&amp;L'!D3</f>
-        <v>46112</v>
+        <v>44196</v>
       </c>
       <c r="B11" s="71">
         <f t="shared" ref="B11:G11" si="0">B8+B9-B10</f>
@@ -43569,7 +43561,7 @@
       <c r="E22" s="351"/>
       <c r="F22" s="416">
         <f>PubBalSht!D2</f>
-        <v>46112</v>
+        <v>44196</v>
       </c>
       <c r="G22" s="416"/>
       <c r="H22" s="389"/>
@@ -44441,7 +44433,7 @@
       <c r="D5" s="433"/>
       <c r="E5" s="434">
         <f>Admin!L6</f>
-        <v>45748</v>
+        <v>43831</v>
       </c>
       <c r="F5" s="392"/>
       <c r="G5" s="176" t="s">
@@ -44449,7 +44441,7 @@
       </c>
       <c r="H5" s="434">
         <f>Admin!N7</f>
-        <v>46477</v>
+        <v>44196</v>
       </c>
       <c r="I5" s="435"/>
       <c r="J5" s="161"/>
@@ -44964,7 +44956,7 @@
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="184">
         <f>D33-C33+1</f>
-        <v>365</v>
+        <v>91</v>
       </c>
       <c r="B33" s="182" t="s">
         <v>14</v>
@@ -44979,7 +44971,7 @@
       </c>
       <c r="E33" s="186">
         <f>Admin!K6</f>
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="F33" s="164">
         <f>IF(K28&gt;0,K28*A33/A35,0)</f>
@@ -45007,7 +44999,7 @@
     <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="184">
         <f>MAX(0,D34-C34+1)</f>
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="B34" s="182" t="s">
         <v>14</v>
@@ -45022,7 +45014,7 @@
       </c>
       <c r="E34" s="186">
         <f>Admin!K7</f>
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="F34" s="164">
         <f>IF(K28&gt;0,K28*A34/A35,0)</f>
@@ -48191,7 +48183,7 @@
       <c r="A33" s="198"/>
       <c r="B33" s="576">
         <f>Admin!L6</f>
-        <v>45748</v>
+        <v>43831</v>
       </c>
       <c r="C33" s="577"/>
       <c r="D33" s="578"/>
@@ -48205,7 +48197,7 @@
       <c r="L33" s="198"/>
       <c r="M33" s="576">
         <f>Admin!N7</f>
-        <v>46477</v>
+        <v>44196</v>
       </c>
       <c r="N33" s="577"/>
       <c r="O33" s="578"/>
@@ -52765,7 +52757,7 @@
       </c>
       <c r="C126" s="545">
         <f>CorporationTax!E33</f>
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D126" s="546"/>
       <c r="E126" s="546"/>

--- a/packages/GB Accounts Company 2020-12-31 (Dec20) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2020-12-31 (Dec20) Excel 2007/Financialaccounts.xlsx
@@ -55397,7 +55397,7 @@
         <v>150</v>
       </c>
       <c r="AA177" s="522" t="str">
-        <f>IF((CorporationTax!H15+CorporationTax!H17)&gt;0,CorporationTax!H15+CorporationTax!H17," ")</f>
+        <f>IF((CorporationTax!I15+CorporationTax!I17)&gt;0,CorporationTax!I15+CorporationTax!I17," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AB177" s="522"/>
@@ -55415,7 +55415,7 @@
         <v>150</v>
       </c>
       <c r="AL177" s="522" t="str">
-        <f>IF(CorporationTax!H18&lt;&gt;0,CorporationTax!H18," ")</f>
+        <f>IF(CorporationTax!I18&lt;&gt;0,CorporationTax!I18," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AM177" s="522"/>
@@ -55507,7 +55507,7 @@
         <v>150</v>
       </c>
       <c r="AA179" s="522" t="str">
-        <f>IF(CorporationTax!H16&gt;0,CorporationTax!H16," ")</f>
+        <f>IF(CorporationTax!I16&gt;0,CorporationTax!I16," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AB179" s="522"/>

--- a/packages/GB Accounts Company 2020-12-31 (Dec20) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2020-12-31 (Dec20) Excel 2007/Financialaccounts.xlsx
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="626">
   <si>
     <t>Depreciation</t>
   </si>
@@ -2159,6 +2159,12 @@
   </si>
   <si>
     <t>(Small profits rate)</t>
+  </si>
+  <si>
+    <t>Copyright (C) 2006-2026 DIY Accounting Limited</t>
+  </si>
+  <si>
+    <t>Licensed under the PolyForm Internal Use License 1.0.0 with an additional grant for accountants. Free to use, source available: https://spreadsheets.diyaccounting.co.uk</t>
   </si>
 </sst>
 </file>
@@ -11957,7 +11963,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R86"/>
+  <dimension ref="A1:R89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="11" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="0.83203125" style="6" customWidth="1"/>
@@ -13448,6 +13454,16 @@
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
+    </row>
+    <row r="88">
+      <c r="B88" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="s">
+        <v>625</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="19">

--- a/packages/GB Accounts Company 2020-12-31 (Dec20) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2020-12-31 (Dec20) Excel 2007/Financialaccounts.xlsx
@@ -12112,9 +12112,13 @@
       </c>
       <c r="M6" s="348"/>
       <c r="N6" s="170"/>
-      <c r="O6" s="151"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
+      <c r="O6" s="338" t="inlineStr">
+        <is>
+          <t>Franked investment income</t>
+        </is>
+      </c>
+      <c r="P6" s="339"/>
+      <c r="Q6" s="11"/>
       <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.15">
@@ -13466,7 +13470,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="G10:K10"/>
     <mergeCell ref="E5:H5"/>
@@ -13485,6 +13489,7 @@
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="O5:P5"/>
+    <mergeCell ref="O6:P6"/>
     <mergeCell ref="J6:K6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -16259,7 +16264,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.5" style="256" customWidth="1"/>
@@ -16383,7 +16388,7 @@
       <c r="P4" s="253"/>
       <c r="Q4" s="253"/>
     </row>
-    <row r="5" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="253"/>
       <c r="B5" s="330">
         <f>DATE(YEAR(B6),MONTH(B6),1)</f>
@@ -16413,8 +16418,28 @@
         <v>623</v>
       </c>
       <c r="Q5" s="255"/>
-    </row>
-    <row r="6" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R5" s="253" t="inlineStr">
+        <is>
+          <t>(Main rate %)</t>
+        </is>
+      </c>
+      <c r="S5" s="253" t="inlineStr">
+        <is>
+          <t>(Relief fraction)</t>
+        </is>
+      </c>
+      <c r="T5" s="253" t="inlineStr">
+        <is>
+          <t>(Relief lower limit)</t>
+        </is>
+      </c>
+      <c r="U5" s="253" t="inlineStr">
+        <is>
+          <t>(Relief upper limit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="253"/>
       <c r="B6" s="330">
         <f>DATE(YEAR(B8),MONTH(B8),1)-1</f>
@@ -16457,8 +16482,20 @@
       <c r="Q6" s="255" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R6" s="310">
+        <v>19</v>
+      </c>
+      <c r="S6" s="262">
+        <v>0</v>
+      </c>
+      <c r="T6" s="262">
+        <v>0</v>
+      </c>
+      <c r="U6" s="262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="253"/>
       <c r="B7" s="330">
         <f>DATE(YEAR(B8),MONTH(B8),1)</f>
@@ -16500,6 +16537,18 @@
       </c>
       <c r="Q7" s="255" t="s">
         <v>268</v>
+      </c>
+      <c r="R7" s="310">
+        <v>19</v>
+      </c>
+      <c r="S7" s="262">
+        <v>0</v>
+      </c>
+      <c r="T7" s="262">
+        <v>0</v>
+      </c>
+      <c r="U7" s="262">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16521,23 +16570,15 @@
         <v>18</v>
       </c>
       <c r="H8" s="253"/>
-      <c r="I8" s="185" t="inlineStr">
-        <is>
-          <t>Corporation Tax main rate</t>
-        </is>
-      </c>
+      <c r="I8" s="185"/>
       <c r="J8" s="253"/>
       <c r="K8" s="253"/>
       <c r="L8" s="253"/>
       <c r="M8" s="253"/>
       <c r="N8" s="253"/>
       <c r="O8" s="253"/>
-      <c r="P8" s="310">
-        <v>19</v>
-      </c>
-      <c r="Q8" s="255" t="s">
-        <v>268</v>
-      </c>
+      <c r="P8" s="310"/>
+      <c r="Q8" s="255"/>
     </row>
     <row r="9" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="253"/>
@@ -16551,11 +16592,7 @@
       <c r="F9" s="253"/>
       <c r="G9" s="255"/>
       <c r="H9" s="253"/>
-      <c r="I9" s="185" t="inlineStr">
-        <is>
-          <t>Marginal relief fraction</t>
-        </is>
-      </c>
+      <c r="I9" s="185"/>
       <c r="J9" s="253"/>
       <c r="K9" s="253"/>
       <c r="L9" s="262" t="s">
@@ -16566,9 +16603,7 @@
         <v>521</v>
       </c>
       <c r="O9" s="263"/>
-      <c r="P9" s="262">
-        <v>0</v>
-      </c>
+      <c r="P9" s="262"/>
       <c r="Q9" s="255"/>
     </row>
     <row r="10" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16645,20 +16680,14 @@
       <c r="F12" s="253"/>
       <c r="G12" s="255"/>
       <c r="H12" s="253"/>
-      <c r="I12" s="185" t="inlineStr">
-        <is>
-          <t>Marginal relief lower limit</t>
-        </is>
-      </c>
+      <c r="I12" s="185"/>
       <c r="J12" s="253"/>
       <c r="K12" s="253"/>
       <c r="L12" s="253"/>
       <c r="M12" s="265"/>
       <c r="N12" s="255"/>
       <c r="O12" s="253"/>
-      <c r="P12" s="262">
-        <v>0</v>
-      </c>
+      <c r="P12" s="262"/>
       <c r="Q12" s="255"/>
     </row>
     <row r="13" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16677,20 +16706,14 @@
         <v>268</v>
       </c>
       <c r="H13" s="253"/>
-      <c r="I13" s="185" t="inlineStr">
-        <is>
-          <t>Marginal relief upper limit</t>
-        </is>
-      </c>
+      <c r="I13" s="185"/>
       <c r="J13" s="253"/>
       <c r="K13" s="253"/>
       <c r="L13" s="253"/>
       <c r="M13" s="253"/>
       <c r="N13" s="253"/>
       <c r="O13" s="253"/>
-      <c r="P13" s="262">
-        <v>0</v>
-      </c>
+      <c r="P13" s="262"/>
       <c r="Q13" s="253"/>
     </row>
     <row r="14" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -44899,7 +44922,11 @@
     </row>
     <row r="29" spans="1:12" s="40" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A29" s="159"/>
-      <c r="B29" s="39"/>
+      <c r="B29" s="306" t="inlineStr">
+        <is>
+          <t>Add franked investment income (exempt distributions received)</t>
+        </is>
+      </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
       <c r="E29" s="157"/>
@@ -44908,12 +44935,19 @@
       <c r="H29" s="162"/>
       <c r="I29" s="161"/>
       <c r="J29" s="161"/>
-      <c r="K29" s="176"/>
+      <c r="K29" s="252">
+        <f>OpenAccounts!Q6</f>
+        <v>0</v>
+      </c>
       <c r="L29" s="39"/>
     </row>
     <row r="30" spans="1:12" s="40" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A30" s="158"/>
-      <c r="B30" s="39"/>
+      <c r="B30" s="306" t="inlineStr">
+        <is>
+          <t>Augmented profits, which the marginal relief limits are tested against</t>
+        </is>
+      </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
       <c r="E30" s="177"/>
@@ -44922,7 +44956,10 @@
       <c r="H30" s="162"/>
       <c r="I30" s="161"/>
       <c r="J30" s="161"/>
-      <c r="K30" s="161"/>
+      <c r="K30" s="252">
+        <f>K28+K29</f>
+        <v>0</v>
+      </c>
       <c r="L30" s="39"/>
     </row>
     <row r="31" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -44994,7 +45031,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="441">
-        <f>IF(F33&lt;=Admin!$P$12*A33/A35,Admin!P6,Admin!$P$8)</f>
+        <f>IF(K30*A33/A35&lt;=Admin!$T$6*A33/A35/(1+Admin!$P$14),Admin!P6,Admin!$R$6)</f>
         <v>19</v>
       </c>
       <c r="H33" s="442"/>
@@ -45008,7 +45045,7 @@
       </c>
       <c r="K33" s="161"/>
       <c r="L33" s="38">
-        <f>IF(AND(F33&gt;Admin!$P$12*A33/A35,F33&lt;Admin!$P$13*A33/A35),(Admin!$P$13*A33/A35-F33)*Admin!$P$9,0)</f>
+        <f>IF(AND(K30*A33/A35&gt;Admin!$T$6*A33/A35/(1+Admin!$P$14),K30*A33/A35&lt;Admin!$U$6*A33/A35/(1+Admin!$P$14)),(Admin!$U$6*A33/A35/(1+Admin!$P$14)-K30*A33/A35)*F33/(K30*A33/A35)*Admin!$S$6,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -45037,7 +45074,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="441">
-        <f>IF(F34&lt;=Admin!$P$12*A34/A35,Admin!P7,Admin!$P$8)</f>
+        <f>IF(K30*A34/A35&lt;=Admin!$T$7*A34/A35/(1+Admin!$P$14),Admin!P7,Admin!$R$7)</f>
         <v>19</v>
       </c>
       <c r="H34" s="442"/>
@@ -45051,7 +45088,7 @@
       </c>
       <c r="K34" s="161"/>
       <c r="L34" s="38">
-        <f>IF(AND(F34&gt;Admin!$P$12*A34/A35,F34&lt;Admin!$P$13*A34/A35),(Admin!$P$13*A34/A35-F34)*Admin!$P$9,0)</f>
+        <f>IF(AND(K30*A34/A35&gt;Admin!$T$7*A34/A35/(1+Admin!$P$14),K30*A34/A35&lt;Admin!$U$7*A34/A35/(1+Admin!$P$14)),(Admin!$U$7*A34/A35/(1+Admin!$P$14)-K30*A34/A35)*F34/(K30*A34/A35)*Admin!$S$7,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -52198,7 +52235,10 @@
       <c r="Y114" s="210" t="s">
         <v>150</v>
       </c>
-      <c r="Z114" s="514"/>
+      <c r="Z114" s="514">
+        <f>CorporationTax!K29</f>
+        <v>0</v>
+      </c>
       <c r="AA114" s="514"/>
       <c r="AB114" s="514"/>
       <c r="AC114" s="514"/>
@@ -52397,7 +52437,10 @@
         <v>40</v>
       </c>
       <c r="X118" s="553"/>
-      <c r="Y118" s="560"/>
+      <c r="Y118" s="560">
+        <f>Admin!$P$14</f>
+        <v>0</v>
+      </c>
       <c r="Z118" s="561"/>
       <c r="AA118" s="562"/>
       <c r="AB118" s="198"/>
@@ -52495,7 +52538,10 @@
         <v>41</v>
       </c>
       <c r="X120" s="553"/>
-      <c r="Y120" s="560"/>
+      <c r="Y120" s="560" t="str">
+        <f>IF(CorporationTax!A34&gt;0,Admin!$P$14," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="Z120" s="561"/>
       <c r="AA120" s="562"/>
       <c r="AB120" s="198"/>
